--- a/hall/resources/sample/VisitorQualityAcquisition.xlsx
+++ b/hall/resources/sample/VisitorQualityAcquisition.xlsx
@@ -140,7 +140,7 @@
     <t>int</t>
   </si>
   <si>
-    <t>list&lt;list&lt;int&gt;{_}&gt;{|}</t>
+    <t>map&lt;int{_}long&gt;{|}</t>
   </si>
   <si>
     <t>string</t>
@@ -371,12 +371,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/hall/resources/sample/VisitorQualityAcquisition.xlsx
+++ b/hall/resources/sample/VisitorQualityAcquisition.xlsx
@@ -106,12 +106,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+这个不作为实际产出，实际的掉落产出与出现的游客配置表挂钩；这个只作为前端的显示用</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
   <si>
     <t>序号ID</t>
   </si>
@@ -137,6 +159,9 @@
     <t>客户端资源</t>
   </si>
   <si>
+    <t>奖励显示</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -167,12 +192,18 @@
     <t>icon</t>
   </si>
   <si>
+    <t>RewardDisplay</t>
+  </si>
+  <si>
     <t>1025101_100|1025102_100|1025103_100|1025104_100|1025105_100|1025106_100</t>
   </si>
   <si>
     <t>白</t>
   </si>
   <si>
+    <t>1024008_2|1024009_2|1024010_2</t>
+  </si>
+  <si>
     <t>1025201_100|1025202_100|1025203_100|1025204_100|1025205_100|1025206_100</t>
   </si>
   <si>
@@ -191,10 +222,16 @@
     <t>紫</t>
   </si>
   <si>
+    <t>1024008_2|1024009_2|1024010_2|1024001_1</t>
+  </si>
+  <si>
     <t>1025501_100|1025502_100|1025503_100|1025504_100|1025505_100|1025506_100</t>
   </si>
   <si>
     <t>金</t>
+  </si>
+  <si>
+    <t>1024008_2|1024009_2|1024010_2|1024001_1|1022505_10</t>
   </si>
 </sst>
 </file>
@@ -1401,8 +1438,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:I34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="22.375" customWidth="1"/>
     <col min="3" max="3" width="13.25" customWidth="1"/>
@@ -1411,9 +1448,10 @@
     <col min="6" max="6" width="12.5" customWidth="1"/>
     <col min="7" max="7" width="17.875" customWidth="1"/>
     <col min="8" max="8" width="15.625" customWidth="1"/>
+    <col min="9" max="9" width="23.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1438,62 +1476,71 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:8">
+        <v>18</v>
+      </c>
+      <c r="I3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" spans="1:9">
       <c r="A5" s="4">
         <v>10001</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D5">
         <v>10</v>
@@ -1504,16 +1551,19 @@
       <c r="F5">
         <v>100</v>
       </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:8">
+      <c r="I5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:9">
       <c r="A6" s="4">
         <v>20001</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -1524,16 +1574,19 @@
       <c r="F6">
         <v>200</v>
       </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:8">
+      <c r="I6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="1:9">
       <c r="A7" s="4">
         <v>30001</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -1544,16 +1597,19 @@
       <c r="F7">
         <v>300</v>
       </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:8">
+      <c r="I7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:9">
       <c r="A8" s="4">
         <v>40001</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>10</v>
@@ -1564,16 +1620,19 @@
       <c r="F8">
         <v>400</v>
       </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:8">
+      <c r="I8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:9">
       <c r="A9" s="4">
         <v>50001</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D9">
         <v>10</v>
@@ -1584,32 +1643,35 @@
       <c r="F9">
         <v>500</v>
       </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:8">
+      <c r="I9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:9">
       <c r="A10" s="4"/>
       <c r="B10" s="6"/>
     </row>
-    <row r="11" ht="16.5" spans="1:8">
+    <row r="11" ht="16.5" spans="1:9">
       <c r="A11" s="4"/>
       <c r="B11" s="6"/>
     </row>
-    <row r="12" ht="16.5" spans="1:8">
+    <row r="12" ht="16.5" spans="1:9">
       <c r="A12" s="4"/>
       <c r="B12" s="6"/>
     </row>
-    <row r="13" ht="16.5" spans="1:8">
+    <row r="13" ht="16.5" spans="1:9">
       <c r="A13" s="4"/>
       <c r="B13" s="6"/>
     </row>
-    <row r="14" ht="16.5" spans="1:8">
+    <row r="14" ht="16.5" spans="1:9">
       <c r="A14" s="4"/>
       <c r="B14" s="6"/>
     </row>
-    <row r="15" ht="16.5" spans="1:8">
+    <row r="15" ht="16.5" spans="1:9">
       <c r="A15" s="4"/>
       <c r="B15" s="6"/>
     </row>
-    <row r="16" ht="16.5" spans="1:8">
+    <row r="16" ht="16.5" spans="1:9">
       <c r="A16" s="4"/>
       <c r="B16" s="6"/>
     </row>

--- a/hall/resources/sample/VisitorQualityAcquisition.xlsx
+++ b/hall/resources/sample/VisitorQualityAcquisition.xlsx
@@ -38,7 +38,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -61,7 +61,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -84,7 +84,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -106,7 +106,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="41">
   <si>
     <t>序号ID</t>
   </si>
@@ -144,6 +144,12 @@
     <t>品质备注</t>
   </si>
   <si>
+    <t>显示名称</t>
+  </si>
+  <si>
+    <t>显示备注</t>
+  </si>
+  <si>
     <t>单次购买出现数量</t>
   </si>
   <si>
@@ -177,6 +183,9 @@
     <t>VisitorWeight</t>
   </si>
   <si>
+    <t>language</t>
+  </si>
+  <si>
     <t>QuantityPerPurchase</t>
   </si>
   <si>
@@ -201,6 +210,9 @@
     <t>白</t>
   </si>
   <si>
+    <t>普通游客</t>
+  </si>
+  <si>
     <t>1024008_2|1024009_2|1024010_2</t>
   </si>
   <si>
@@ -210,18 +222,27 @@
     <t>绿</t>
   </si>
   <si>
+    <t>优秀游客</t>
+  </si>
+  <si>
     <t>1025301_100|1025302_100|1025303_100|1025304_100|1025305_100|1025306_100</t>
   </si>
   <si>
     <t>蓝</t>
   </si>
   <si>
+    <t>精英游客</t>
+  </si>
+  <si>
     <t>1025401_100|1025402_100|1025403_100|1025404_100|1025405_100|1025406_100</t>
   </si>
   <si>
     <t>紫</t>
   </si>
   <si>
+    <t>卓越游客</t>
+  </si>
+  <si>
     <t>1024008_2|1024009_2|1024010_2|1024001_1</t>
   </si>
   <si>
@@ -229,6 +250,9 @@
   </si>
   <si>
     <t>金</t>
+  </si>
+  <si>
+    <t>VIP游客</t>
   </si>
   <si>
     <t>1024008_2|1024009_2|1024010_2|1024001_1|1022505_10</t>
@@ -244,7 +268,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -262,6 +286,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -754,137 +784,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -902,6 +932,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -958,11 +994,18 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="19">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="9" tint="-0.25"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.4"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1159,25 +1202,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="7"/>
-      <tableStyleElement type="headerRow" dxfId="6"/>
-      <tableStyleElement type="totalRow" dxfId="5"/>
-      <tableStyleElement type="firstColumn" dxfId="4"/>
-      <tableStyleElement type="lastColumn" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" dxfId="8"/>
+      <tableStyleElement type="headerRow" dxfId="7"/>
+      <tableStyleElement type="totalRow" dxfId="6"/>
+      <tableStyleElement type="firstColumn" dxfId="5"/>
+      <tableStyleElement type="lastColumn" dxfId="4"/>
+      <tableStyleElement type="firstRowStripe" dxfId="3"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="2"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="17"/>
-      <tableStyleElement type="totalRow" dxfId="16"/>
-      <tableStyleElement type="firstRowStripe" dxfId="15"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
-      <tableStyleElement type="pageFieldValues" dxfId="8"/>
+      <tableStyleElement type="headerRow" dxfId="18"/>
+      <tableStyleElement type="totalRow" dxfId="17"/>
+      <tableStyleElement type="firstRowStripe" dxfId="16"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="15"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="14"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="12"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="11"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="10"/>
+      <tableStyleElement type="pageFieldValues" dxfId="9"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1438,20 +1481,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="22.375" customWidth="1"/>
     <col min="3" max="3" width="13.25" customWidth="1"/>
     <col min="4" max="4" width="15.75" customWidth="1"/>
-    <col min="5" max="5" width="12.75" customWidth="1"/>
-    <col min="6" max="6" width="12.5" customWidth="1"/>
-    <col min="7" max="7" width="17.875" customWidth="1"/>
-    <col min="8" max="8" width="15.625" customWidth="1"/>
-    <col min="9" max="9" width="23.75" customWidth="1"/>
+    <col min="5" max="5" width="11.625" customWidth="1"/>
+    <col min="6" max="6" width="15.75" customWidth="1"/>
+    <col min="7" max="7" width="12.75" customWidth="1"/>
+    <col min="8" max="8" width="12.5" customWidth="1"/>
+    <col min="9" max="9" width="17.875" customWidth="1"/>
+    <col min="10" max="10" width="15.625" customWidth="1"/>
+    <col min="11" max="11" width="23.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1473,283 +1518,328 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
       <c r="I2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>11</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
       <c r="I3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:9">
+        <v>20</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" spans="1:11">
       <c r="A5" s="4">
         <v>10001</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5">
+        <v>24</v>
+      </c>
+      <c r="D5" s="6">
+        <v>4010060</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5">
         <v>10</v>
       </c>
-      <c r="E5">
+      <c r="G5">
         <v>1</v>
       </c>
-      <c r="F5">
-        <v>100</v>
-      </c>
-      <c r="I5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:9">
+      <c r="H5">
+        <v>100</v>
+      </c>
+      <c r="K5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:11">
       <c r="A6" s="4">
         <v>20001</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6">
+        <v>28</v>
+      </c>
+      <c r="D6" s="6">
+        <v>4010061</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6">
         <v>10</v>
       </c>
-      <c r="E6">
+      <c r="G6">
         <v>1</v>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>200</v>
       </c>
-      <c r="I6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:9">
+      <c r="K6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="1:11">
       <c r="A7" s="4">
         <v>30001</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="6">
+        <v>4010062</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>300</v>
+      </c>
+      <c r="K7" t="s">
         <v>26</v>
       </c>
-      <c r="D7">
-        <v>10</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>300</v>
-      </c>
-      <c r="I7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:9">
+    </row>
+    <row r="8" ht="16.5" spans="1:11">
       <c r="A8" s="4">
         <v>40001</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8">
+        <v>34</v>
+      </c>
+      <c r="D8" s="6">
+        <v>4010063</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8">
         <v>10</v>
       </c>
-      <c r="E8">
+      <c r="G8">
         <v>1</v>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>400</v>
       </c>
-      <c r="I8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:9">
+      <c r="K8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:11">
       <c r="A9" s="4">
         <v>50001</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9">
+        <v>38</v>
+      </c>
+      <c r="D9" s="6">
+        <v>4010064</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9">
         <v>10</v>
       </c>
-      <c r="E9">
+      <c r="G9">
         <v>1</v>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>500</v>
       </c>
-      <c r="I9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:9">
+      <c r="K9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:11">
       <c r="A10" s="4"/>
-      <c r="B10" s="6"/>
-    </row>
-    <row r="11" ht="16.5" spans="1:9">
+      <c r="B10" s="8"/>
+    </row>
+    <row r="11" ht="16.5" spans="1:11">
       <c r="A11" s="4"/>
-      <c r="B11" s="6"/>
-    </row>
-    <row r="12" ht="16.5" spans="1:9">
+      <c r="B11" s="8"/>
+    </row>
+    <row r="12" ht="16.5" spans="1:11">
       <c r="A12" s="4"/>
-      <c r="B12" s="6"/>
-    </row>
-    <row r="13" ht="16.5" spans="1:9">
+      <c r="B12" s="8"/>
+    </row>
+    <row r="13" ht="16.5" spans="1:11">
       <c r="A13" s="4"/>
-      <c r="B13" s="6"/>
-    </row>
-    <row r="14" ht="16.5" spans="1:9">
+      <c r="B13" s="8"/>
+    </row>
+    <row r="14" ht="16.5" spans="1:11">
       <c r="A14" s="4"/>
-      <c r="B14" s="6"/>
-    </row>
-    <row r="15" ht="16.5" spans="1:9">
+      <c r="B14" s="8"/>
+    </row>
+    <row r="15" ht="16.5" spans="1:11">
       <c r="A15" s="4"/>
-      <c r="B15" s="6"/>
-    </row>
-    <row r="16" ht="16.5" spans="1:9">
+      <c r="B15" s="8"/>
+    </row>
+    <row r="16" ht="16.5" spans="1:11">
       <c r="A16" s="4"/>
-      <c r="B16" s="6"/>
+      <c r="B16" s="8"/>
     </row>
     <row r="17" ht="16.5" spans="1:2">
       <c r="A17" s="4"/>
-      <c r="B17" s="6"/>
+      <c r="B17" s="8"/>
     </row>
     <row r="18" ht="16.5" spans="1:2">
       <c r="A18" s="4"/>
-      <c r="B18" s="6"/>
+      <c r="B18" s="8"/>
     </row>
     <row r="19" ht="16.5" spans="1:2">
       <c r="A19" s="4"/>
-      <c r="B19" s="6"/>
+      <c r="B19" s="8"/>
     </row>
     <row r="20" ht="16.5" spans="1:2">
       <c r="A20" s="4"/>
-      <c r="B20" s="6"/>
+      <c r="B20" s="8"/>
     </row>
     <row r="21" ht="16.5" spans="1:2">
       <c r="A21" s="4"/>
-      <c r="B21" s="6"/>
+      <c r="B21" s="8"/>
     </row>
     <row r="22" ht="16.5" spans="1:2">
       <c r="A22" s="4"/>
-      <c r="B22" s="6"/>
+      <c r="B22" s="8"/>
     </row>
     <row r="23" ht="16.5" spans="1:2">
       <c r="A23" s="4"/>
-      <c r="B23" s="6"/>
+      <c r="B23" s="8"/>
     </row>
     <row r="24" ht="16.5" spans="1:2">
       <c r="A24" s="4"/>
-      <c r="B24" s="6"/>
+      <c r="B24" s="8"/>
     </row>
     <row r="25" ht="16.5" spans="1:2">
       <c r="A25" s="4"/>
-      <c r="B25" s="6"/>
+      <c r="B25" s="8"/>
     </row>
     <row r="26" ht="16.5" spans="1:2">
       <c r="A26" s="4"/>
-      <c r="B26" s="6"/>
+      <c r="B26" s="8"/>
     </row>
     <row r="27" ht="16.5" spans="1:2">
       <c r="A27" s="4"/>
-      <c r="B27" s="6"/>
+      <c r="B27" s="8"/>
     </row>
     <row r="28" ht="16.5" spans="1:2">
       <c r="A28" s="4"/>
-      <c r="B28" s="6"/>
+      <c r="B28" s="8"/>
     </row>
     <row r="29" ht="16.5" spans="1:2">
       <c r="A29" s="4"/>
-      <c r="B29" s="6"/>
+      <c r="B29" s="8"/>
     </row>
     <row r="30" ht="16.5" spans="1:2">
       <c r="A30" s="4"/>
-      <c r="B30" s="6"/>
+      <c r="B30" s="8"/>
     </row>
     <row r="31" ht="16.5" spans="1:2">
       <c r="A31" s="4"/>
-      <c r="B31" s="6"/>
+      <c r="B31" s="8"/>
     </row>
     <row r="32" ht="16.5" spans="1:2">
       <c r="A32" s="4"/>
-      <c r="B32" s="6"/>
+      <c r="B32" s="8"/>
     </row>
     <row r="33" ht="16.5" spans="1:2">
       <c r="A33" s="4"/>
-      <c r="B33" s="6"/>
+      <c r="B33" s="8"/>
     </row>
     <row r="34" ht="16.5" spans="1:2">
       <c r="A34" s="4"/>
-      <c r="B34" s="6"/>
+      <c r="B34" s="8"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B34">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5:E9">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/hall/resources/sample/VisitorQualityAcquisition.xlsx
+++ b/hall/resources/sample/VisitorQualityAcquisition.xlsx
@@ -133,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="46">
   <si>
     <t>序号ID</t>
   </si>
@@ -213,6 +213,9 @@
     <t>普通游客</t>
   </si>
   <si>
+    <t>ykpztb_1.png</t>
+  </si>
+  <si>
     <t>1024008_2|1024009_2|1024010_2</t>
   </si>
   <si>
@@ -225,6 +228,9 @@
     <t>优秀游客</t>
   </si>
   <si>
+    <t>ykpztb_2.png</t>
+  </si>
+  <si>
     <t>1025301_100|1025302_100|1025303_100|1025304_100|1025305_100|1025306_100</t>
   </si>
   <si>
@@ -234,6 +240,9 @@
     <t>精英游客</t>
   </si>
   <si>
+    <t>ykpztb_3.png</t>
+  </si>
+  <si>
     <t>1025401_100|1025402_100|1025403_100|1025404_100|1025405_100|1025406_100</t>
   </si>
   <si>
@@ -243,6 +252,9 @@
     <t>卓越游客</t>
   </si>
   <si>
+    <t>ykpztb_4.png</t>
+  </si>
+  <si>
     <t>1024008_2|1024009_2|1024010_2|1024001_1</t>
   </si>
   <si>
@@ -253,6 +265,9 @@
   </si>
   <si>
     <t>VIP游客</t>
+  </si>
+  <si>
+    <t>ykpztb_5.png</t>
   </si>
   <si>
     <t>1024008_2|1024009_2|1024010_2|1024001_1|1022505_10</t>
@@ -1614,8 +1629,11 @@
       <c r="H5">
         <v>100</v>
       </c>
+      <c r="J5" t="s">
+        <v>26</v>
+      </c>
       <c r="K5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:11">
@@ -1623,16 +1641,16 @@
         <v>20001</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" s="6">
         <v>4010061</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6">
         <v>10</v>
@@ -1643,8 +1661,11 @@
       <c r="H6">
         <v>200</v>
       </c>
+      <c r="J6" t="s">
+        <v>31</v>
+      </c>
       <c r="K6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:11">
@@ -1652,16 +1673,16 @@
         <v>30001</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7" s="6">
         <v>4010062</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F7">
         <v>10</v>
@@ -1672,8 +1693,11 @@
       <c r="H7">
         <v>300</v>
       </c>
+      <c r="J7" t="s">
+        <v>35</v>
+      </c>
       <c r="K7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:11">
@@ -1681,16 +1705,16 @@
         <v>40001</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D8" s="6">
         <v>4010063</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F8">
         <v>10</v>
@@ -1701,8 +1725,11 @@
       <c r="H8">
         <v>400</v>
       </c>
+      <c r="J8" t="s">
+        <v>39</v>
+      </c>
       <c r="K8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:11">
@@ -1710,16 +1737,16 @@
         <v>50001</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D9" s="6">
         <v>4010064</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F9">
         <v>10</v>
@@ -1730,8 +1757,11 @@
       <c r="H9">
         <v>500</v>
       </c>
+      <c r="J9" t="s">
+        <v>44</v>
+      </c>
       <c r="K9" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:11">
